--- a/reports/pdf_rolling5_20260909.xlsx
+++ b/reports/pdf_rolling5_20260909.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,482억   ·   현금 41억(0.9%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 16종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,482억   ·   현금 21억(0.5%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 16종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1271,7 +1271,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,518억   ·   현금 87억(2.5%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 4종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,518억   ·   현금 44억(1.2%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1564,7 +1564,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 69억(2.7%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 10종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 34억(1.4%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 10종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -2061,7 +2061,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,991억   ·   현금 8억(0.4%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 6종목  /  매도 11종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,991억   ·   현금 4억(0.2%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 6종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2554,7 +2554,7 @@
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 270억   ·   현금 2억(0.9%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 9종목  /  매도 11종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 270억   ·   현금 1억(0.5%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 9종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B61" s="4" t="n"/>
@@ -2972,23 +2972,23 @@
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-21462000</v>
+        <v>-61530000</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.84%</t>
+          <t>3.71%→3.48%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>219→213</t>
+          <t>97→91</t>
         </is>
       </c>
     </row>
@@ -3016,23 +3016,23 @@
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-61530000</v>
+        <v>-21462000</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>3.71%→3.48%</t>
+          <t>2.92%→2.84%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>97→91</t>
+          <t>219→213</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 498억   ·   현금 8억(1.7%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 498억   ·   현금 4억(0.8%)      오늘 2026-09-09  vs  5일전 2026-09-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B76" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260909.xlsx
+++ b/reports/pdf_rolling5_20260909.xlsx
@@ -1131,23 +1131,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1199730000</v>
+        <v>818496000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.14%</t>
+          <t>0.97%→1.07%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>39→51</t>
+          <t>58→70</t>
         </is>
       </c>
       <c r="G17" s="17" t="n"/>
@@ -1159,23 +1159,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>818496000</v>
+        <v>1199730000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.07%</t>
+          <t>0.94%→1.14%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>58→70</t>
+          <t>39→51</t>
         </is>
       </c>
       <c r="G18" s="17" t="n"/>
@@ -1873,23 +1873,23 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>로보티즈  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2943660000</v>
+        <v>2653440000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.18%</t>
+          <t>2.19%→3.55%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>0→15</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -1917,23 +1917,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈  (신규)</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>2653440000</v>
+        <v>2943660000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>2.19%→3.55%</t>
+          <t>0.00%→1.18%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -2972,23 +2972,23 @@
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-61530000</v>
+        <v>-21462000</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>3.71%→3.48%</t>
+          <t>2.92%→2.84%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>97→91</t>
+          <t>219→213</t>
         </is>
       </c>
     </row>
@@ -3016,23 +3016,23 @@
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-21462000</v>
+        <v>-61530000</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.84%</t>
+          <t>3.71%→3.48%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>219→213</t>
+          <t>97→91</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260909.xlsx
+++ b/reports/pdf_rolling5_20260909.xlsx
@@ -1131,23 +1131,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>818496000</v>
+        <v>1199730000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.07%</t>
+          <t>0.94%→1.14%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>58→70</t>
+          <t>39→51</t>
         </is>
       </c>
       <c r="G17" s="17" t="n"/>
@@ -1159,23 +1159,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1199730000</v>
+        <v>818496000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.14%</t>
+          <t>0.97%→1.07%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>39→51</t>
+          <t>58→70</t>
         </is>
       </c>
       <c r="G18" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260909.xlsx
+++ b/reports/pdf_rolling5_20260909.xlsx
@@ -2972,23 +2972,23 @@
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-21462000</v>
+        <v>-61530000</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.84%</t>
+          <t>3.71%→3.48%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>219→213</t>
+          <t>97→91</t>
         </is>
       </c>
     </row>
@@ -3016,23 +3016,23 @@
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-61530000</v>
+        <v>-21462000</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>3.71%→3.48%</t>
+          <t>2.92%→2.84%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>97→91</t>
+          <t>219→213</t>
         </is>
       </c>
     </row>
